--- a/ZHOUYAN/ep1_1.xlsx
+++ b/ZHOUYAN/ep1_1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\N2_2025_12\ZHOUYAN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FC5A9D9-5D21-43A3-BED4-329613E4665B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5766E2A-1950-45A7-BF8F-50C6DCE29E80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2340" yWindow="1605" windowWidth="20880" windowHeight="19995" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="284">
   <si>
     <t>Fre</t>
   </si>
@@ -567,6 +567,612 @@
   </si>
   <si>
     <t>总觉得有点带刺</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>方</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>かた</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>“人”的礼貌说法</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>人生</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>じんせい</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>って</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>所谓…</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>不公平</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ふこうへい</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>時給</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>じきゅう</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>パート</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>兼职</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>辞める</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>やめる</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>辞掉</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>しゃべる</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>说话、聊天</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>レジ閉め</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>结账清算</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>間もなく</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>まもなく</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>马上、很快</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>主任</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>しゅにん</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>切っとく</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>きっとく</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>先打卡「切っておく」の口語形</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>豚バラ</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ぶたばら</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>五花肉</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>タイムセール</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>限时特卖</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ティッシュ</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>纸巾；面巾纸</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>トイレットペーパー</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>卫生纸;厕纸</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>洗剤</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>せんざい</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>洗涤剂;清洁剂</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>やべっ</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>糟糕、坏了</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>「やばい」の口語</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>お呼び出し</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>およびだし</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>呼叫、廣播找人</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>申し上げます</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>もうしあげます</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>「言う</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>・する</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>」自谦</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>伝える</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>つたえる</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>传达</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ございます</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>“ある”的郑重语</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>至急</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>しきゅう</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>火速、赶快</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>従業員</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>じゅうぎょういん</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>店员、员工</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>泥棒</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>どろぼう</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>小偷;窃贼</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>やってねえ</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>没做、没干（“やっていない”的极粗鲁口语）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ウソつけ</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>撒谎、胡说八道（带有命令语气的斥责）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>こらあ</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>喂！、嘿！（斥责时的怒喝，常见于警察或不良少年）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>やばいよ</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>不好了、不得了</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>やられた</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>被弄了、被干掉了</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>落ち着いて</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>おちついて</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>冷静、沉着</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>離せよ</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>はなせよ</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>放开、松手</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>てめえ</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>你这家伙</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>出さないで</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ださないで</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>不要发出、不要做出（“出す”的否定中顿）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ちょうだい</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>请……（女性化、带有亲昵或威严的请求）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>たった今</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>たったいま</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>从现在这一刻起</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>口紅</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>くちべに</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>黙ってて</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>だまってて</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>保持沉默、不开口（「黙っている」の口語形）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>話 合わせて</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>はなし あわせて</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>配合我（把话圆上）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>结尾用"て"作为轻微的命令/请求</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>遭う</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>あう</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>受害、遭遇</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>約束</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>やくそく</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>约定、预约</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>予約-&gt;よやく</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>勤務先</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>きんむさき</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>工作单位</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>お知り合い</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>おしりあい</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>认识的人</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>～なんです</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>是…(理由や説明を強調する形）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ウソつく</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>撒谎</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>困ります</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>こまります</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>困扰、为难</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>つく</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>～ちゃった</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>「～てしまった」の口語形</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>不倫</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ふりん</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>出轨、婚外情</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>バレる</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>暴露；败露；被发现</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>冗談じゃない</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>じょうだんじゃない</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>别开玩笑了 / 岂有此理</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>最低</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>さいてい</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>最差劲、人品极差</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>不潔</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ふけつ</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>肮脏、不洁、恶心（道德上的）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>冷たい</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>つめたい</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>冷淡的、冷酷的</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>寒い-&gt;さむい</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>拾う</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ひろう</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>おいた</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>“～ておく”的过去式</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>似合い</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>にあい</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>相配；合适；协调</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -574,7 +1180,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -595,6 +1201,13 @@
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Yu Gothic"/>
+      <family val="2"/>
+      <charset val="128"/>
     </font>
   </fonts>
   <fills count="2">
@@ -945,7 +1558,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E58"/>
+  <dimension ref="A1:E115"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="9" customWidth="1"/>
@@ -1755,6 +2368,813 @@
         <v>137</v>
       </c>
       <c r="E58" s="3"/>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A59">
+        <v>0</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="C59" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="D59" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="E59" s="3"/>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A60">
+        <v>0</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C60" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="D60" s="3"/>
+      <c r="E60" s="3"/>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A61">
+        <v>0</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C61" s="3"/>
+      <c r="D61" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="E61" s="3"/>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A62">
+        <v>0</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="C62" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="D62" s="3"/>
+      <c r="E62" s="3"/>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A63">
+        <v>0</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="C63" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="D63" s="3"/>
+      <c r="E63" s="3"/>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A64">
+        <v>0</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="C64" s="3"/>
+      <c r="D64" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="E64" s="3"/>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A65">
+        <v>0</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="C65" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="D65" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="E65" s="3"/>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A66">
+        <v>0</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="C66" s="3"/>
+      <c r="D66" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="E66" s="3"/>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A67">
+        <v>0</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="C67" s="3"/>
+      <c r="D67" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="E67" s="3"/>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A68">
+        <v>0</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="C68" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="D68" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="E68" s="3"/>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A69">
+        <v>0</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="C69" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="D69" s="3"/>
+      <c r="E69" s="3"/>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A70">
+        <v>0</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="C70" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="D70" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="E70" s="3"/>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A71">
+        <v>0</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="C71" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="D71" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="E71" s="3"/>
+    </row>
+    <row r="72" spans="1:5" ht="27" x14ac:dyDescent="0.15">
+      <c r="A72">
+        <v>0</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="C72" s="3"/>
+      <c r="D72" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="E72" s="3"/>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A73">
+        <v>0</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="C73" s="3"/>
+      <c r="D73" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="E73" s="3"/>
+    </row>
+    <row r="74" spans="1:5" ht="27" x14ac:dyDescent="0.15">
+      <c r="A74">
+        <v>0</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="C74" s="3"/>
+      <c r="D74" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="E74" s="3"/>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A75">
+        <v>0</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C75" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="D75" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="E75" s="3"/>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A76">
+        <v>0</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="C76" s="3"/>
+      <c r="D76" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="E76" s="3" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A77">
+        <v>0</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="C77" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="D77" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="E77" s="3"/>
+    </row>
+    <row r="78" spans="1:5" ht="27" x14ac:dyDescent="0.4">
+      <c r="A78">
+        <v>0</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="C78" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="D78" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="E78" s="3"/>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A79">
+        <v>0</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="C79" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="D79" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="E79" s="3"/>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A80">
+        <v>0</v>
+      </c>
+      <c r="B80" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="C80" s="3"/>
+      <c r="D80" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="E80" s="3"/>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A81">
+        <v>0</v>
+      </c>
+      <c r="B81" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="C81" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="D81" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="E81" s="3"/>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A82">
+        <v>0</v>
+      </c>
+      <c r="B82" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="C82" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="D82" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="E82" s="3"/>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A83">
+        <v>0</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="C83" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="D83" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="E83" s="3"/>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A84">
+        <v>0</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="C84" s="3"/>
+      <c r="D84" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="E84" s="3"/>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A85">
+        <v>0</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="C85" s="3"/>
+      <c r="D85" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="E85" s="3"/>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A86">
+        <v>0</v>
+      </c>
+      <c r="B86" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="C86" s="3"/>
+      <c r="D86" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="E86" s="3"/>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A87">
+        <v>0</v>
+      </c>
+      <c r="B87" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="C87" s="3"/>
+      <c r="D87" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="E87" s="3"/>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A88">
+        <v>0</v>
+      </c>
+      <c r="B88" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="C88" s="3"/>
+      <c r="D88" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="E88" s="3"/>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A89">
+        <v>0</v>
+      </c>
+      <c r="B89" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="C89" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="D89" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="E89" s="3"/>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A90">
+        <v>0</v>
+      </c>
+      <c r="B90" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="C90" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="D90" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="E90" s="3"/>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A91">
+        <v>0</v>
+      </c>
+      <c r="B91" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="C91" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D91" s="3"/>
+      <c r="E91" s="3"/>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A92">
+        <v>0</v>
+      </c>
+      <c r="B92" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="C92" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="D92" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="E92" s="3"/>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A93">
+        <v>0</v>
+      </c>
+      <c r="B93" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="C93" s="3"/>
+      <c r="D93" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="E93" s="3"/>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A94">
+        <v>0</v>
+      </c>
+      <c r="B94" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="C94" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="D94" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="E94" s="3"/>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A95">
+        <v>0</v>
+      </c>
+      <c r="B95" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="C95" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="D95" s="3"/>
+      <c r="E95" s="3"/>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A96">
+        <v>0</v>
+      </c>
+      <c r="B96" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="C96" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="D96" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="E96" s="3"/>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A97">
+        <v>0</v>
+      </c>
+      <c r="B97" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="C97" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="D97" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="E97" s="3" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A98">
+        <v>0</v>
+      </c>
+      <c r="B98" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="C98" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="D98" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="E98" s="3"/>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A99">
+        <v>0</v>
+      </c>
+      <c r="B99" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="C99" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="D99" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="E99" s="3" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A100">
+        <v>0</v>
+      </c>
+      <c r="B100" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="C100" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="D100" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="E100" s="3"/>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A101">
+        <v>0</v>
+      </c>
+      <c r="B101" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="C101" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="D101" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="E101" s="3"/>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A102">
+        <v>0</v>
+      </c>
+      <c r="B102" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="C102" s="3"/>
+      <c r="D102" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="E102" s="3"/>
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A103">
+        <v>0</v>
+      </c>
+      <c r="B103" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="C103" s="3"/>
+      <c r="D103" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="E103" s="3"/>
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A104">
+        <v>0</v>
+      </c>
+      <c r="B104" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="C104" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="D104" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="E104" s="3"/>
+    </row>
+    <row r="105" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A105">
+        <v>0</v>
+      </c>
+      <c r="B105" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="C105" s="3"/>
+      <c r="D105" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="E105" s="3"/>
+    </row>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A106">
+        <v>0</v>
+      </c>
+      <c r="B106" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="C106" s="3"/>
+      <c r="D106" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="E106" s="3"/>
+    </row>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A107">
+        <v>0</v>
+      </c>
+      <c r="B107" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="C107" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="D107" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="E107" s="3"/>
+    </row>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A108">
+        <v>0</v>
+      </c>
+      <c r="B108" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="C108" s="3"/>
+      <c r="D108" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="E108" s="3"/>
+    </row>
+    <row r="109" spans="1:5" ht="27" x14ac:dyDescent="0.15">
+      <c r="A109">
+        <v>0</v>
+      </c>
+      <c r="B109" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="C109" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="D109" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="E109" s="3"/>
+    </row>
+    <row r="110" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A110">
+        <v>0</v>
+      </c>
+      <c r="B110" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="C110" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="D110" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="E110" s="3"/>
+    </row>
+    <row r="111" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A111">
+        <v>0</v>
+      </c>
+      <c r="B111" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="C111" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="D111" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="E111" s="3"/>
+    </row>
+    <row r="112" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A112">
+        <v>0</v>
+      </c>
+      <c r="B112" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="C112" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="D112" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="E112" s="3" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A113">
+        <v>0</v>
+      </c>
+      <c r="B113" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="C113" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="D113" s="3"/>
+      <c r="E113" s="3"/>
+    </row>
+    <row r="114" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A114">
+        <v>0</v>
+      </c>
+      <c r="B114" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="C114" s="3"/>
+      <c r="D114" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="E114" s="3"/>
+    </row>
+    <row r="115" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A115">
+        <v>0</v>
+      </c>
+      <c r="B115" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="C115" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="D115" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="E115" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>

--- a/ZHOUYAN/ep1_1.xlsx
+++ b/ZHOUYAN/ep1_1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\N2_2025_12\ZHOUYAN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5766E2A-1950-45A7-BF8F-50C6DCE29E80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6064B8BD-FA78-4DF5-BBC5-5E17AEBD171B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2340" yWindow="1605" windowWidth="20880" windowHeight="19995" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="20880" windowHeight="19995" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="284">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="460" uniqueCount="449">
   <si>
     <t>Fre</t>
   </si>
@@ -1173,6 +1173,666 @@
   </si>
   <si>
     <t>相配；合适；协调</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>間違える</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>まちがえる</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>被疑者</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ひぎしゃ</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>嫌疑人</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>少年</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>しょうねん</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>未成年男性</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>上等だ</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>じょうとうだ</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>正合我意、放马过来</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>親御さん</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>おやごさん</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>他父母、他家长</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>うちの生徒</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>せいと</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>我校学生</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ご迷惑</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ごめいわく</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>添麻烦</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>おかけしました</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>「かける」的自谦</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>かける</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>(1)悬挂，挂上 (2)添，带来(麻烦) (3)花费</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>指導</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>しどう</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>指导、管教、教育</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>示談</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>じだん</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>私了、和解</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>結構です</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>けっこうです</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>足够了、可以、没问题</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>結婚</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>けっこん</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ちゃんと</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>好好地、认真地</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>反省</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>はんせい</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>おわび</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>道歉、致歉</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>便所</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>べんじょ</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>おケガ</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>伤、受伤</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>一応</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>いちおう</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>姑且、起码、先（保险起见）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>診る</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>みる</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>看病、诊察</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>治療</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ちりょう</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>治疗</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>お送りします</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>おおくりします</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>送（您）回去</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>どいてよ</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>让开/别挡道</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>神様</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>かみさま</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>上帝；老天爷</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>してしまったこと</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>做下了（无法挽回的事）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>心から</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>こころから</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>すてきな</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>极好的、漂亮的、完美的</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>おうち</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>房子、家庭</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>旦那さん</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>だんなさん</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>丈夫（他人の夫への敬称）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ばれる</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>地獄</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>じごく</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>落ちます</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>おちます</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>掉落、坠落</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>転ぶ</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ころぶ</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>摔倒、跌倒</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>よける</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>避开；躲避</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>とした</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>打算…、尝试做…</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ヒビ</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>骨裂，裂紋</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>可是、但是</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>いいから</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>好了好了、没关系、别说了（用于制止对方）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>どうせ</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>反正（带有一种宿命论或轻蔑的语气）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>んだし</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>因为…嘛</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>結果が出る</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>けっかがでる</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>出结果</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>きっと</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>一定、必定</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ごはん</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>饭、用餐</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>連絡先</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>れんらくさき</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>联系方式</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>聞いておいて</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>提前问好</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>よかった</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>幸亏、太好了</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>無事に帰れた？</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>平安到家了吗</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>妻</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>つま</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>お誘いした</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>おさそいした</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>邀请了(自谦)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>申し訳ありませんでした</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>もうしわけ</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>非常抱歉</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>世間知らず</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>せけんしらず</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>不懂人情世故</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>懲りる</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>こりる</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>吸取教訓</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>これからも</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>今后也</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>仲よく</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>なかよく</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>友好地、和睦地</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>突然ごめんなさいね</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>とつぜん</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>こういうところ</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>这种地方 / 这方面</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>堅苦しい</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>かたくるしい</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>呆板、严谨</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>いいかげん</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>敷衍、馬虎、不认真</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ほら</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>你看（引起注意，带有一种“你应该记得吧”的语气）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>話し合い</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>はなしあい</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>协商、谈话</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>関係</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>かんけい</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>参りません</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>まいりません</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>我不会去的</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>謝る</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>あやまる</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>道歉；认错；谢罪</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>１週間</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>いっしゅうかん</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>停学</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ていがく</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>処分</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>しょぶん</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>もうすぐ</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>～だし</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>而且、再加上</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>卒業</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>そつぎょう</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>半年</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>はんとし</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1558,7 +2218,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E115"/>
+  <dimension ref="A1:E185"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="9" customWidth="1"/>
@@ -2857,324 +3517,556 @@
       <c r="E93" s="3"/>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A94">
-        <v>0</v>
-      </c>
-      <c r="B94" s="2" t="s">
-        <v>224</v>
-      </c>
-      <c r="C94" s="3" t="s">
-        <v>225</v>
-      </c>
-      <c r="D94" s="3" t="s">
-        <v>226</v>
-      </c>
+      <c r="B94" s="2"/>
+      <c r="C94" s="3"/>
+      <c r="D94" s="3"/>
       <c r="E94" s="3"/>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A95">
-        <v>0</v>
-      </c>
-      <c r="B95" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="C95" s="3" t="s">
-        <v>228</v>
-      </c>
+      <c r="B95" s="2"/>
+      <c r="C95" s="3"/>
       <c r="D95" s="3"/>
       <c r="E95" s="3"/>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A96">
-        <v>0</v>
-      </c>
-      <c r="B96" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="C96" s="3" t="s">
-        <v>230</v>
-      </c>
-      <c r="D96" s="3" t="s">
-        <v>231</v>
-      </c>
+      <c r="B96" s="2"/>
+      <c r="C96" s="3"/>
+      <c r="D96" s="3"/>
       <c r="E96" s="3"/>
     </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A97">
-        <v>0</v>
-      </c>
-      <c r="B97" s="2" t="s">
-        <v>232</v>
-      </c>
-      <c r="C97" s="3" t="s">
-        <v>233</v>
-      </c>
-      <c r="D97" s="3" t="s">
-        <v>234</v>
-      </c>
-      <c r="E97" s="3" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A98">
-        <v>0</v>
-      </c>
-      <c r="B98" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="C98" s="3" t="s">
-        <v>237</v>
-      </c>
-      <c r="D98" s="3" t="s">
-        <v>238</v>
-      </c>
+    <row r="97" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B97" s="2"/>
+      <c r="C97" s="3"/>
+      <c r="D97" s="3"/>
+      <c r="E97" s="3"/>
+    </row>
+    <row r="98" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B98" s="2"/>
+      <c r="C98" s="3"/>
+      <c r="D98" s="3"/>
       <c r="E98" s="3"/>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A99">
-        <v>0</v>
-      </c>
-      <c r="B99" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="C99" s="3" t="s">
-        <v>240</v>
-      </c>
-      <c r="D99" s="3" t="s">
-        <v>241</v>
-      </c>
-      <c r="E99" s="3" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A100">
-        <v>0</v>
-      </c>
-      <c r="B100" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="C100" s="3" t="s">
-        <v>244</v>
-      </c>
-      <c r="D100" s="3" t="s">
-        <v>245</v>
-      </c>
+    <row r="99" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B99" s="2"/>
+      <c r="C99" s="3"/>
+      <c r="D99" s="3"/>
+      <c r="E99" s="3"/>
+    </row>
+    <row r="100" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B100" s="2"/>
+      <c r="C100" s="3"/>
+      <c r="D100" s="3"/>
       <c r="E100" s="3"/>
     </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A101">
-        <v>0</v>
-      </c>
-      <c r="B101" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="C101" s="3" t="s">
-        <v>247</v>
-      </c>
-      <c r="D101" s="3" t="s">
-        <v>248</v>
-      </c>
+    <row r="101" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B101" s="2"/>
+      <c r="C101" s="3"/>
+      <c r="D101" s="3"/>
       <c r="E101" s="3"/>
     </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A102">
-        <v>0</v>
-      </c>
-      <c r="B102" s="2" t="s">
-        <v>249</v>
-      </c>
+    <row r="102" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B102" s="2"/>
       <c r="C102" s="3"/>
-      <c r="D102" s="3" t="s">
-        <v>250</v>
-      </c>
+      <c r="D102" s="3"/>
       <c r="E102" s="3"/>
     </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A103">
-        <v>0</v>
-      </c>
-      <c r="B103" s="2" t="s">
-        <v>251</v>
-      </c>
+    <row r="103" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B103" s="2"/>
       <c r="C103" s="3"/>
-      <c r="D103" s="3" t="s">
-        <v>252</v>
-      </c>
+      <c r="D103" s="3"/>
       <c r="E103" s="3"/>
     </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A104">
-        <v>0</v>
-      </c>
-      <c r="B104" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="C104" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="D104" s="3" t="s">
-        <v>255</v>
-      </c>
+    <row r="104" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B104" s="2"/>
+      <c r="C104" s="3"/>
+      <c r="D104" s="3"/>
       <c r="E104" s="3"/>
     </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A105">
-        <v>0</v>
-      </c>
-      <c r="B105" s="2" t="s">
-        <v>256</v>
-      </c>
+    <row r="105" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B105" s="2"/>
       <c r="C105" s="3"/>
-      <c r="D105" s="3" t="s">
-        <v>252</v>
-      </c>
+      <c r="D105" s="3"/>
       <c r="E105" s="3"/>
     </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A106">
-        <v>0</v>
-      </c>
-      <c r="B106" s="2" t="s">
-        <v>257</v>
-      </c>
+    <row r="106" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B106" s="2"/>
       <c r="C106" s="3"/>
-      <c r="D106" s="3" t="s">
-        <v>258</v>
-      </c>
+      <c r="D106" s="3"/>
       <c r="E106" s="3"/>
     </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A107">
-        <v>0</v>
-      </c>
-      <c r="B107" s="2" t="s">
-        <v>259</v>
-      </c>
-      <c r="C107" s="3" t="s">
-        <v>260</v>
-      </c>
-      <c r="D107" s="3" t="s">
-        <v>261</v>
-      </c>
+    <row r="107" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B107" s="2"/>
+      <c r="C107" s="3"/>
+      <c r="D107" s="3"/>
       <c r="E107" s="3"/>
     </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A108">
-        <v>0</v>
-      </c>
-      <c r="B108" s="2" t="s">
-        <v>262</v>
-      </c>
+    <row r="108" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B108" s="2"/>
       <c r="C108" s="3"/>
-      <c r="D108" s="3" t="s">
-        <v>263</v>
-      </c>
+      <c r="D108" s="3"/>
       <c r="E108" s="3"/>
     </row>
-    <row r="109" spans="1:5" ht="27" x14ac:dyDescent="0.15">
-      <c r="A109">
-        <v>0</v>
-      </c>
-      <c r="B109" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="C109" s="3" t="s">
-        <v>265</v>
-      </c>
-      <c r="D109" s="3" t="s">
-        <v>266</v>
-      </c>
+    <row r="109" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B109" s="2"/>
+      <c r="C109" s="3"/>
+      <c r="D109" s="3"/>
       <c r="E109" s="3"/>
     </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A110">
-        <v>0</v>
-      </c>
-      <c r="B110" s="2" t="s">
-        <v>267</v>
-      </c>
-      <c r="C110" s="3" t="s">
-        <v>268</v>
-      </c>
-      <c r="D110" s="3" t="s">
-        <v>269</v>
-      </c>
+    <row r="110" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B110" s="2"/>
+      <c r="C110" s="3"/>
+      <c r="D110" s="3"/>
       <c r="E110" s="3"/>
     </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A111">
-        <v>0</v>
-      </c>
-      <c r="B111" s="2" t="s">
-        <v>270</v>
-      </c>
-      <c r="C111" s="3" t="s">
-        <v>271</v>
-      </c>
-      <c r="D111" s="3" t="s">
-        <v>272</v>
-      </c>
+    <row r="111" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B111" s="2"/>
+      <c r="C111" s="3"/>
+      <c r="D111" s="3"/>
       <c r="E111" s="3"/>
     </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A112">
-        <v>0</v>
-      </c>
-      <c r="B112" s="2" t="s">
-        <v>273</v>
-      </c>
-      <c r="C112" s="3" t="s">
-        <v>274</v>
-      </c>
-      <c r="D112" s="3" t="s">
-        <v>275</v>
-      </c>
-      <c r="E112" s="3" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A113">
-        <v>0</v>
-      </c>
-      <c r="B113" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="C113" s="3" t="s">
-        <v>278</v>
-      </c>
+    <row r="112" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B112" s="2"/>
+      <c r="C112" s="3"/>
+      <c r="D112" s="3"/>
+      <c r="E112" s="3"/>
+    </row>
+    <row r="113" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B113" s="2"/>
+      <c r="C113" s="3"/>
       <c r="D113" s="3"/>
       <c r="E113" s="3"/>
     </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A114">
-        <v>0</v>
-      </c>
-      <c r="B114" s="2" t="s">
-        <v>279</v>
-      </c>
+    <row r="114" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B114" s="2"/>
       <c r="C114" s="3"/>
-      <c r="D114" s="3" t="s">
-        <v>280</v>
-      </c>
+      <c r="D114" s="3"/>
       <c r="E114" s="3"/>
     </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A115">
-        <v>0</v>
-      </c>
-      <c r="B115" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="C115" s="3" t="s">
-        <v>282</v>
-      </c>
-      <c r="D115" s="3" t="s">
-        <v>283</v>
-      </c>
+    <row r="115" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B115" s="2"/>
+      <c r="C115" s="3"/>
+      <c r="D115" s="3"/>
       <c r="E115" s="3"/>
+    </row>
+    <row r="116" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B116" s="2"/>
+      <c r="C116" s="3"/>
+      <c r="D116" s="3"/>
+      <c r="E116" s="3"/>
+    </row>
+    <row r="117" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B117" s="2"/>
+      <c r="C117" s="3"/>
+      <c r="D117" s="3"/>
+      <c r="E117" s="3"/>
+    </row>
+    <row r="118" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B118" s="2"/>
+      <c r="C118" s="3"/>
+      <c r="D118" s="3"/>
+      <c r="E118" s="3"/>
+    </row>
+    <row r="119" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B119" s="2"/>
+      <c r="C119" s="3"/>
+      <c r="D119" s="3"/>
+      <c r="E119" s="3"/>
+    </row>
+    <row r="120" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B120" s="2"/>
+      <c r="C120" s="3"/>
+      <c r="D120" s="3"/>
+      <c r="E120" s="3"/>
+    </row>
+    <row r="121" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B121" s="2"/>
+      <c r="C121" s="3"/>
+      <c r="D121" s="3"/>
+      <c r="E121" s="3"/>
+    </row>
+    <row r="122" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B122" s="2"/>
+      <c r="C122" s="3"/>
+      <c r="D122" s="3"/>
+      <c r="E122" s="3"/>
+    </row>
+    <row r="123" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B123" s="2"/>
+      <c r="C123" s="3"/>
+      <c r="D123" s="3"/>
+      <c r="E123" s="3"/>
+    </row>
+    <row r="124" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B124" s="2"/>
+      <c r="C124" s="3"/>
+      <c r="D124" s="3"/>
+      <c r="E124" s="3"/>
+    </row>
+    <row r="125" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B125" s="2"/>
+      <c r="C125" s="3"/>
+      <c r="D125" s="3"/>
+      <c r="E125" s="3"/>
+    </row>
+    <row r="126" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B126" s="2"/>
+      <c r="C126" s="3"/>
+      <c r="D126" s="3"/>
+      <c r="E126" s="3"/>
+    </row>
+    <row r="127" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B127" s="2"/>
+      <c r="C127" s="3"/>
+      <c r="D127" s="3"/>
+      <c r="E127" s="3"/>
+    </row>
+    <row r="128" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B128" s="2"/>
+      <c r="C128" s="3"/>
+      <c r="D128" s="3"/>
+      <c r="E128" s="3"/>
+    </row>
+    <row r="129" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B129" s="2"/>
+      <c r="C129" s="3"/>
+      <c r="D129" s="3"/>
+      <c r="E129" s="3"/>
+    </row>
+    <row r="130" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B130" s="2"/>
+      <c r="C130" s="3"/>
+      <c r="D130" s="3"/>
+      <c r="E130" s="3"/>
+    </row>
+    <row r="131" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B131" s="2"/>
+      <c r="C131" s="3"/>
+      <c r="D131" s="3"/>
+      <c r="E131" s="3"/>
+    </row>
+    <row r="132" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B132" s="2"/>
+      <c r="C132" s="3"/>
+      <c r="D132" s="3"/>
+      <c r="E132" s="3"/>
+    </row>
+    <row r="133" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B133" s="2"/>
+      <c r="C133" s="3"/>
+      <c r="D133" s="3"/>
+      <c r="E133" s="3"/>
+    </row>
+    <row r="134" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B134" s="2"/>
+      <c r="C134" s="3"/>
+      <c r="D134" s="3"/>
+      <c r="E134" s="3"/>
+    </row>
+    <row r="135" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B135" s="2"/>
+      <c r="C135" s="3"/>
+      <c r="D135" s="3"/>
+      <c r="E135" s="3"/>
+    </row>
+    <row r="136" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B136" s="2"/>
+      <c r="C136" s="3"/>
+      <c r="D136" s="3"/>
+      <c r="E136" s="3"/>
+    </row>
+    <row r="137" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B137" s="2"/>
+      <c r="C137" s="3"/>
+      <c r="D137" s="3"/>
+      <c r="E137" s="3"/>
+    </row>
+    <row r="138" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B138" s="2"/>
+      <c r="C138" s="3"/>
+      <c r="D138" s="3"/>
+      <c r="E138" s="3"/>
+    </row>
+    <row r="139" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B139" s="2"/>
+      <c r="C139" s="3"/>
+      <c r="D139" s="3"/>
+      <c r="E139" s="3"/>
+    </row>
+    <row r="140" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B140" s="2"/>
+      <c r="C140" s="3"/>
+      <c r="D140" s="3"/>
+      <c r="E140" s="3"/>
+    </row>
+    <row r="141" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B141" s="2"/>
+      <c r="C141" s="3"/>
+      <c r="D141" s="3"/>
+      <c r="E141" s="3"/>
+    </row>
+    <row r="142" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B142" s="2"/>
+      <c r="C142" s="3"/>
+      <c r="D142" s="3"/>
+      <c r="E142" s="3"/>
+    </row>
+    <row r="143" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B143" s="2"/>
+      <c r="C143" s="3"/>
+      <c r="D143" s="3"/>
+      <c r="E143" s="3"/>
+    </row>
+    <row r="144" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B144" s="2"/>
+      <c r="C144" s="3"/>
+      <c r="D144" s="3"/>
+      <c r="E144" s="3"/>
+    </row>
+    <row r="145" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B145" s="2"/>
+      <c r="C145" s="3"/>
+      <c r="D145" s="3"/>
+      <c r="E145" s="3"/>
+    </row>
+    <row r="146" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B146" s="2"/>
+      <c r="C146" s="3"/>
+      <c r="D146" s="3"/>
+      <c r="E146" s="3"/>
+    </row>
+    <row r="147" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B147" s="2"/>
+      <c r="C147" s="3"/>
+      <c r="D147" s="3"/>
+      <c r="E147" s="3"/>
+    </row>
+    <row r="148" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B148" s="2"/>
+      <c r="C148" s="3"/>
+      <c r="D148" s="3"/>
+      <c r="E148" s="3"/>
+    </row>
+    <row r="149" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B149" s="2"/>
+      <c r="C149" s="3"/>
+      <c r="D149" s="3"/>
+      <c r="E149" s="3"/>
+    </row>
+    <row r="150" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B150" s="2"/>
+      <c r="C150" s="3"/>
+      <c r="D150" s="3"/>
+      <c r="E150" s="3"/>
+    </row>
+    <row r="151" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B151" s="2"/>
+      <c r="C151" s="3"/>
+      <c r="D151" s="3"/>
+      <c r="E151" s="3"/>
+    </row>
+    <row r="152" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B152" s="2"/>
+      <c r="C152" s="3"/>
+      <c r="D152" s="3"/>
+      <c r="E152" s="3"/>
+    </row>
+    <row r="153" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B153" s="2"/>
+      <c r="C153" s="3"/>
+      <c r="D153" s="3"/>
+      <c r="E153" s="3"/>
+    </row>
+    <row r="154" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B154" s="2"/>
+      <c r="C154" s="3"/>
+      <c r="D154" s="3"/>
+      <c r="E154" s="3"/>
+    </row>
+    <row r="155" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B155" s="2"/>
+      <c r="C155" s="3"/>
+      <c r="D155" s="3"/>
+      <c r="E155" s="3"/>
+    </row>
+    <row r="156" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B156" s="2"/>
+      <c r="C156" s="3"/>
+      <c r="D156" s="3"/>
+      <c r="E156" s="3"/>
+    </row>
+    <row r="157" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B157" s="2"/>
+      <c r="C157" s="3"/>
+      <c r="D157" s="3"/>
+      <c r="E157" s="3"/>
+    </row>
+    <row r="158" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B158" s="2"/>
+      <c r="C158" s="3"/>
+      <c r="D158" s="3"/>
+      <c r="E158" s="3"/>
+    </row>
+    <row r="159" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B159" s="2"/>
+      <c r="C159" s="3"/>
+      <c r="D159" s="3"/>
+      <c r="E159" s="3"/>
+    </row>
+    <row r="160" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B160" s="2"/>
+      <c r="C160" s="3"/>
+      <c r="D160" s="3"/>
+      <c r="E160" s="3"/>
+    </row>
+    <row r="161" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B161" s="2"/>
+      <c r="C161" s="3"/>
+      <c r="D161" s="3"/>
+      <c r="E161" s="3"/>
+    </row>
+    <row r="162" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B162" s="2"/>
+      <c r="C162" s="3"/>
+      <c r="D162" s="3"/>
+      <c r="E162" s="3"/>
+    </row>
+    <row r="163" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B163" s="2"/>
+      <c r="C163" s="3"/>
+      <c r="D163" s="3"/>
+      <c r="E163" s="3"/>
+    </row>
+    <row r="164" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B164" s="2"/>
+      <c r="C164" s="3"/>
+      <c r="D164" s="3"/>
+      <c r="E164" s="3"/>
+    </row>
+    <row r="165" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B165" s="2"/>
+      <c r="C165" s="3"/>
+      <c r="D165" s="3"/>
+      <c r="E165" s="3"/>
+    </row>
+    <row r="166" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B166" s="2"/>
+      <c r="C166" s="3"/>
+      <c r="D166" s="3"/>
+      <c r="E166" s="3"/>
+    </row>
+    <row r="167" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B167" s="2"/>
+      <c r="C167" s="3"/>
+      <c r="D167" s="3"/>
+      <c r="E167" s="3"/>
+    </row>
+    <row r="168" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B168" s="2"/>
+      <c r="C168" s="3"/>
+      <c r="D168" s="3"/>
+      <c r="E168" s="3"/>
+    </row>
+    <row r="169" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B169" s="2"/>
+      <c r="C169" s="3"/>
+      <c r="D169" s="3"/>
+      <c r="E169" s="3"/>
+    </row>
+    <row r="170" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B170" s="2"/>
+      <c r="C170" s="3"/>
+      <c r="D170" s="3"/>
+      <c r="E170" s="3"/>
+    </row>
+    <row r="171" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B171" s="2"/>
+      <c r="C171" s="3"/>
+      <c r="D171" s="3"/>
+      <c r="E171" s="3"/>
+    </row>
+    <row r="172" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B172" s="2"/>
+      <c r="C172" s="3"/>
+      <c r="D172" s="3"/>
+      <c r="E172" s="3"/>
+    </row>
+    <row r="173" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B173" s="2"/>
+      <c r="C173" s="3"/>
+      <c r="D173" s="3"/>
+      <c r="E173" s="3"/>
+    </row>
+    <row r="174" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B174" s="2"/>
+      <c r="C174" s="3"/>
+      <c r="D174" s="3"/>
+      <c r="E174" s="3"/>
+    </row>
+    <row r="175" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B175" s="2"/>
+      <c r="C175" s="3"/>
+      <c r="D175" s="3"/>
+      <c r="E175" s="3"/>
+    </row>
+    <row r="176" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B176" s="2"/>
+      <c r="C176" s="3"/>
+      <c r="D176" s="3"/>
+      <c r="E176" s="3"/>
+    </row>
+    <row r="177" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B177" s="2"/>
+      <c r="C177" s="3"/>
+      <c r="D177" s="3"/>
+      <c r="E177" s="3"/>
+    </row>
+    <row r="178" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B178" s="2"/>
+      <c r="C178" s="3"/>
+      <c r="D178" s="3"/>
+      <c r="E178" s="3"/>
+    </row>
+    <row r="179" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B179" s="2"/>
+      <c r="C179" s="3"/>
+      <c r="D179" s="3"/>
+      <c r="E179" s="3"/>
+    </row>
+    <row r="180" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B180" s="2"/>
+      <c r="C180" s="3"/>
+      <c r="D180" s="3"/>
+      <c r="E180" s="3"/>
+    </row>
+    <row r="181" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B181" s="2"/>
+      <c r="C181" s="3"/>
+      <c r="D181" s="3"/>
+      <c r="E181" s="3"/>
+    </row>
+    <row r="182" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B182" s="2"/>
+      <c r="C182" s="3"/>
+      <c r="D182" s="3"/>
+      <c r="E182" s="3"/>
+    </row>
+    <row r="183" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B183" s="2"/>
+      <c r="C183" s="3"/>
+      <c r="D183" s="3"/>
+      <c r="E183" s="3"/>
+    </row>
+    <row r="184" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B184" s="2"/>
+      <c r="C184" s="3"/>
+      <c r="D184" s="3"/>
+      <c r="E184" s="3"/>
+    </row>
+    <row r="185" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="B185" s="3"/>
+      <c r="C185" s="3"/>
+      <c r="D185" s="3"/>
+      <c r="E185" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
@@ -3185,9 +4077,1182 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:E93"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="9" style="3" customWidth="1"/>
+    <col min="2" max="2" width="16.625" style="3" customWidth="1"/>
+    <col min="3" max="3" width="17.375" style="3" customWidth="1"/>
+    <col min="4" max="4" width="26.5" style="3" customWidth="1"/>
+    <col min="5" max="5" width="28.875" style="3" customWidth="1"/>
+    <col min="6" max="16384" width="9" style="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A2" s="3">
+        <v>0</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A3" s="3">
+        <v>0</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A4" s="3">
+        <v>0</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="27" x14ac:dyDescent="0.15">
+      <c r="A5" s="3">
+        <v>0</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A6" s="3">
+        <v>0</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A7" s="3">
+        <v>0</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A8" s="3">
+        <v>0</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="27" x14ac:dyDescent="0.15">
+      <c r="A9" s="3">
+        <v>0</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="27" x14ac:dyDescent="0.15">
+      <c r="A10" s="3">
+        <v>0</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A11" s="3">
+        <v>0</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A12" s="3">
+        <v>0</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A13" s="3">
+        <v>0</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="27" x14ac:dyDescent="0.15">
+      <c r="A14" s="3">
+        <v>0</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A15" s="3">
+        <v>0</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A16" s="3">
+        <v>0</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="27" x14ac:dyDescent="0.15">
+      <c r="A17" s="3">
+        <v>0</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A18" s="3">
+        <v>0</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A19" s="3">
+        <v>0</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A20" s="3">
+        <v>0</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A21" s="3">
+        <v>0</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A22" s="3">
+        <v>0</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A23" s="3">
+        <v>0</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A24" s="3">
+        <v>0</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A25" s="3">
+        <v>0</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A26" s="3">
+        <v>0</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A27" s="3">
+        <v>0</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A28" s="3">
+        <v>0</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" ht="27" x14ac:dyDescent="0.15">
+      <c r="A29" s="3">
+        <v>0</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A30" s="3">
+        <v>0</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" ht="27" x14ac:dyDescent="0.15">
+      <c r="A31" s="3">
+        <v>0</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A32" s="3">
+        <v>0</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A33" s="3">
+        <v>0</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>309</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A34" s="3">
+        <v>0</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A35" s="3">
+        <v>0</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A36" s="3">
+        <v>0</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A37" s="3">
+        <v>0</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A38" s="3">
+        <v>0</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A39" s="3">
+        <v>0</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A40" s="3">
+        <v>0</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A41" s="3">
+        <v>0</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A42" s="3">
+        <v>0</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A43" s="3">
+        <v>0</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A44" s="3">
+        <v>0</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" ht="27" x14ac:dyDescent="0.15">
+      <c r="A45" s="3">
+        <v>0</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="D45" s="3" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A46" s="3">
+        <v>0</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="D46" s="3" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A47" s="3">
+        <v>0</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="D47" s="3" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" ht="27" x14ac:dyDescent="0.15">
+      <c r="A48" s="3">
+        <v>0</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="D48" s="3" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A49" s="3">
+        <v>0</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A50" s="3">
+        <v>0</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A51" s="3">
+        <v>0</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="D51" s="3" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A52" s="3">
+        <v>0</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="D52" s="3" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A53" s="3">
+        <v>0</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="D53" s="3" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A54" s="3">
+        <v>0</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A55" s="3">
+        <v>0</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>361</v>
+      </c>
+      <c r="D55" s="3" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A56" s="3">
+        <v>0</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>364</v>
+      </c>
+      <c r="D56" s="3" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A57" s="3">
+        <v>0</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="D57" s="3" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A58" s="3">
+        <v>0</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="D58" s="3" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A59" s="3">
+        <v>0</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="D59" s="3" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A60" s="3">
+        <v>0</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D60" s="3" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A61" s="3">
+        <v>0</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="D61" s="3" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A62" s="3">
+        <v>0</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="D62" s="3" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A63" s="3">
+        <v>0</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="D63" s="3" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" ht="27" x14ac:dyDescent="0.15">
+      <c r="A64" s="3">
+        <v>0</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="C64" s="3" t="s">
+        <v>380</v>
+      </c>
+      <c r="D64" s="3" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A65" s="3">
+        <v>0</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="D65" s="3" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A66" s="3">
+        <v>0</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="D66" s="3" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A67" s="3">
+        <v>0</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="C67" s="3" t="s">
+        <v>387</v>
+      </c>
+      <c r="D67" s="3" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" ht="27" x14ac:dyDescent="0.15">
+      <c r="A68" s="3">
+        <v>0</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="D68" s="3" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A69" s="3">
+        <v>0</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="D69" s="3" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" ht="27" x14ac:dyDescent="0.15">
+      <c r="A70" s="3">
+        <v>0</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="D70" s="3" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A71" s="3">
+        <v>0</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="C71" s="3" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" ht="27" x14ac:dyDescent="0.15">
+      <c r="A72" s="3">
+        <v>0</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>397</v>
+      </c>
+      <c r="C72" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="D72" s="3" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" ht="40.5" x14ac:dyDescent="0.15">
+      <c r="A73" s="3">
+        <v>0</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="C73" s="3" t="s">
+        <v>401</v>
+      </c>
+      <c r="D73" s="3" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" ht="27" x14ac:dyDescent="0.15">
+      <c r="A74" s="3">
+        <v>0</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="C74" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="D74" s="3" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A75" s="3">
+        <v>0</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="C75" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="D75" s="3" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" ht="27" x14ac:dyDescent="0.15">
+      <c r="A76" s="3">
+        <v>0</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="D76" s="3" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A77" s="3">
+        <v>0</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="C77" s="3" t="s">
+        <v>412</v>
+      </c>
+      <c r="D77" s="3" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" ht="40.5" x14ac:dyDescent="0.15">
+      <c r="A78" s="3">
+        <v>0</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="C78" s="3" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" ht="27" x14ac:dyDescent="0.15">
+      <c r="A79" s="3">
+        <v>0</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="D79" s="3" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A80" s="3">
+        <v>0</v>
+      </c>
+      <c r="B80" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="C80" s="3" t="s">
+        <v>419</v>
+      </c>
+      <c r="D80" s="3" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" ht="27" x14ac:dyDescent="0.15">
+      <c r="A81" s="3">
+        <v>0</v>
+      </c>
+      <c r="B81" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="D81" s="3" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A82" s="3">
+        <v>0</v>
+      </c>
+      <c r="B82" s="2" t="s">
+        <v>423</v>
+      </c>
+      <c r="D82" s="3" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A83" s="3">
+        <v>0</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>425</v>
+      </c>
+      <c r="C83" s="3" t="s">
+        <v>426</v>
+      </c>
+      <c r="D83" s="3" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A84" s="3">
+        <v>0</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="C84" s="3" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" ht="27" x14ac:dyDescent="0.15">
+      <c r="A85" s="3">
+        <v>0</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="C85" s="3" t="s">
+        <v>431</v>
+      </c>
+      <c r="D85" s="3" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A86" s="3">
+        <v>0</v>
+      </c>
+      <c r="B86" s="2" t="s">
+        <v>433</v>
+      </c>
+      <c r="C86" s="3" t="s">
+        <v>434</v>
+      </c>
+      <c r="D86" s="3" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A87" s="3">
+        <v>0</v>
+      </c>
+      <c r="B87" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="C87" s="3" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A88" s="3">
+        <v>0</v>
+      </c>
+      <c r="B88" s="2" t="s">
+        <v>438</v>
+      </c>
+      <c r="C88" s="3" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A89" s="3">
+        <v>0</v>
+      </c>
+      <c r="B89" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="C89" s="3" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A90" s="3">
+        <v>0</v>
+      </c>
+      <c r="B90" s="2" t="s">
+        <v>442</v>
+      </c>
+      <c r="D90" s="3" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A91" s="3">
+        <v>0</v>
+      </c>
+      <c r="B91" s="2" t="s">
+        <v>443</v>
+      </c>
+      <c r="D91" s="3" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A92" s="3">
+        <v>0</v>
+      </c>
+      <c r="B92" s="2" t="s">
+        <v>445</v>
+      </c>
+      <c r="C92" s="3" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A93" s="3">
+        <v>0</v>
+      </c>
+      <c r="B93" s="3" t="s">
+        <v>447</v>
+      </c>
+      <c r="C93" s="3" t="s">
+        <v>448</v>
+      </c>
+    </row>
+  </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
